--- a/02_Basic_Excel_for_Data_Analytics/08_Functions.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/08_Functions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D36213-A0A5-4055-89BB-483A5D7C42F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C53C7B9-43CB-4A5D-9189-D901A450F32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Total for Mansi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hike 10 marks of Shivani </t>
   </si>
 </sst>
 </file>
@@ -95,7 +98,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -108,8 +111,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -132,11 +141,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -153,6 +206,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -435,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.54296875" style="1" customWidth="1"/>
@@ -443,7 +508,7 @@
     <col min="6" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -460,7 +525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -480,7 +545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -495,10 +560,10 @@
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="5">
-        <v>45673</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -516,8 +581,16 @@
         <f>DAY(F3)</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H4">
+        <f>YEAR(F3)</f>
+        <v>2026</v>
+      </c>
+      <c r="I4">
+        <f>MONTH(F3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -532,7 +605,7 @@
       </c>
       <c r="E5" s="6"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F8" s="3" t="s">
         <v>8</v>
       </c>
@@ -541,16 +614,16 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G9">
         <f>SUM(C:C)</f>
-        <v>454</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F10" t="s">
         <v>11</v>
       </c>
@@ -559,13 +632,26 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C12" s="1">
-        <f>SUM(B2:B5, 10)</f>
-        <v>178</v>
-      </c>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="8">
+        <f>SUM(B4:D4,10)</f>
+        <v>175</v>
+      </c>
+      <c r="B13" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>